--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京朝阳区东坝万达</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>东坝万达广场一层中庭</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京朝阳区东坝万达</t>
+          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>东坝万达广场一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>深圳市福田区</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京朝阳区东坝万达</t>
+          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>东坝万达广场一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京朝阳区东坝万达</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>东坝万达广场一层中庭</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>深圳市福田区</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京朝阳区东坝万达</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>东坝万达广场一层中庭</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京朝阳区东坝万达</t>
+          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>东坝万达广场一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>深圳市福田区</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京朝阳区东坝万达</t>
+          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>东坝万达广场一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京朝阳区东坝万达</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>东坝万达广场一层中庭</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>深圳市福田区</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>深圳市福田区</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>深圳市福田区</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 5 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
+          <t>连续在档 4 期；历史有闪烁（疑似漏爬，关注下期是否回归）</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11994,22 +11994,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京朝阳区东坝万达</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>东坝万达广场一层中庭</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>小米汽车北京朝阳区东坝万达</t>
+          <t>小米汽车北京市大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>东坝万达广场一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市花都区建设北路</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市花都区建设北路223号</t>
+          <t>龙溪大道502号自编1</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小米汽车广东省广州市花都区建设北路</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1</t>
+          <t>广东省广州市花都区建设北路223号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720_vs_20260727.xlsx
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车许昌M8汽车城销售展厅</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
+          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京房山区熙悦龙湖天街</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车梅州广梅路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清乐成销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
+          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雀园路销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
+          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车梅州广梅路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅县区扶大高新区广梅南路286-2号 → 广东省梅州市梅县区广梅南路286-2号</t>
+          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
+          <t>小鹏汽车乐清乐成销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
+          <t>浙江省温州市乐清市城南街道宁康西路255号 → 浙江省温州市乐清市康宁西路255号(南大产业园)</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车长沙雀园路销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区胜利南路105号 → 河北省张家口市胜利南路105号</t>
+          <t>长沙市天心区雀园路70号 → 湖南省长沙市天心区雀园东路8号东侧4S店一楼103门面</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车楚雄滇中汽车城销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
+          <t>云南省楚雄市程家坝楚雄艺龙特约维修站旁 → 楚雄市滇中汽车城212汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小米汽车北京房山区熙悦龙湖天街</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园 → 河南省洛阳市涧西区建设路152号东方红· 704青创产业园</t>
+          <t>房山熙悦天街B馆一层中庭 → 房山熙悦天街A馆一层中庭</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区金宝乐园南100米路西 → 山东省潍坊市奎文区潍州路2800号</t>
+          <t>天津市东丽区空港经济区环河北路62号 → 天津市东丽区空港经济区汽车园环河北路62号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车许昌M8汽车城销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>宿州市经济开发区西昌南路东侧A522号 → 安徽省宿州市经济开发区西昌南路东侧A522号</t>
+          <t>河南省许昌市魏都区许昌市延安路与陈庄街交叉口西500米路南 → 许昌市魏都区延安路与陈庄街交叉口西300米路北</t>
         </is>
       </c>
     </row>
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>济南济西保时捷中心</t>
+          <t>华为授权体验店（融侨外滩壹号）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>济南保时捷中心</t>
+          <t>华为授权体验店（融侨外滩）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩壹号）</t>
+          <t>济南济西保时捷中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（融侨外滩）</t>
+          <t>济南保时捷中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
